--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561714278</v>
+        <v>46157.93070207787</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93070207787</v>
+        <v>46157.93152469814</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93152469814</v>
+        <v>46157.93393401951</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393401951</v>
+        <v>46157.93707754286</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93707754286</v>
+        <v>46158.28210429073</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210429073</v>
+        <v>46158.29665387002</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29665387002</v>
+        <v>46158.29804506278</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29804506278</v>
+        <v>46158.33381138589</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33381138589</v>
+        <v>46158.36847598083</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Тошпулатоа/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847598083</v>
+        <v>46158.37281363583</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
